--- a/source/9、人数基数/人数基数-5月.xlsx
+++ b/source/9、人数基数/人数基数-5月.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22400" windowHeight="10200"/>
+    <workbookView windowWidth="21550" windowHeight="10200"/>
   </bookViews>
   <sheets>
     <sheet name="人数基数模板" sheetId="1" r:id="rId1"/>
@@ -2445,7 +2445,7 @@
         <v>74</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="D68" s="2">
         <v>288</v>

--- a/source/9、人数基数/人数基数-5月.xlsx
+++ b/source/9、人数基数/人数基数-5月.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="21550" windowHeight="10200"/>
+    <workbookView windowWidth="22400" windowHeight="10200"/>
   </bookViews>
   <sheets>
     <sheet name="人数基数模板" sheetId="1" r:id="rId1"/>
@@ -1328,7 +1328,7 @@
       <c r="D2" s="2">
         <v>889</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>889</v>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       <c r="D3" s="2">
         <v>701</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>701</v>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       <c r="D4" s="2">
         <v>565</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>565</v>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       <c r="D5" s="2">
         <v>629</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>629</v>
       </c>
     </row>
@@ -1394,10 +1394,10 @@
         <v>7</v>
       </c>
       <c r="D6" s="2">
-        <v>432</v>
-      </c>
-      <c r="E6" s="1">
-        <v>432</v>
+        <v>433</v>
+      </c>
+      <c r="E6" s="2">
+        <v>433</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1413,7 +1413,7 @@
       <c r="D7" s="2">
         <v>1786</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>1786</v>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       <c r="D8" s="2">
         <v>1192</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>1192</v>
       </c>
     </row>
@@ -1445,10 +1445,10 @@
         <v>7</v>
       </c>
       <c r="D9" s="2">
-        <v>2350</v>
-      </c>
-      <c r="E9" s="1">
-        <v>2350</v>
+        <v>2351</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2351</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1464,7 +1464,7 @@
       <c r="D10" s="2">
         <v>919</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="2">
         <v>919</v>
       </c>
     </row>
@@ -1479,10 +1479,10 @@
         <v>7</v>
       </c>
       <c r="D11" s="2">
-        <v>1065</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1065</v>
+        <v>1067</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1067</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1498,7 +1498,7 @@
       <c r="D12" s="2">
         <v>509</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
         <v>509</v>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       <c r="D13" s="2">
         <v>808</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>808</v>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       <c r="D14" s="2">
         <v>878</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
         <v>878</v>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       <c r="D15" s="2">
         <v>557</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="2">
         <v>557</v>
       </c>
     </row>
@@ -1564,10 +1564,10 @@
         <v>7</v>
       </c>
       <c r="D16" s="2">
-        <v>1182</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1182</v>
+        <v>1180</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1180</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1581,10 +1581,10 @@
         <v>7</v>
       </c>
       <c r="D17" s="2">
-        <v>878</v>
-      </c>
-      <c r="E17" s="1">
-        <v>878</v>
+        <v>877</v>
+      </c>
+      <c r="E17" s="2">
+        <v>877</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1600,7 +1600,7 @@
       <c r="D18" s="2">
         <v>279</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="2">
         <v>279</v>
       </c>
     </row>
@@ -1615,10 +1615,10 @@
         <v>7</v>
       </c>
       <c r="D19" s="2">
-        <v>936</v>
-      </c>
-      <c r="E19" s="1">
-        <v>936</v>
+        <v>935</v>
+      </c>
+      <c r="E19" s="2">
+        <v>935</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1634,7 +1634,7 @@
       <c r="D20" s="2">
         <v>1146</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="2">
         <v>1146</v>
       </c>
     </row>
@@ -1649,10 +1649,10 @@
         <v>7</v>
       </c>
       <c r="D21" s="2">
-        <v>778</v>
-      </c>
-      <c r="E21" s="1">
-        <v>778</v>
+        <v>781</v>
+      </c>
+      <c r="E21" s="2">
+        <v>781</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1666,10 +1666,10 @@
         <v>7</v>
       </c>
       <c r="D22" s="2">
-        <v>1019</v>
-      </c>
-      <c r="E22" s="1">
-        <v>1019</v>
+        <v>1017</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1017</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1683,10 +1683,10 @@
         <v>7</v>
       </c>
       <c r="D23" s="2">
-        <v>371</v>
-      </c>
-      <c r="E23" s="1">
-        <v>371</v>
+        <v>372</v>
+      </c>
+      <c r="E23" s="2">
+        <v>372</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1700,10 +1700,10 @@
         <v>7</v>
       </c>
       <c r="D24" s="2">
-        <v>475</v>
-      </c>
-      <c r="E24" s="1">
-        <v>475</v>
+        <v>474</v>
+      </c>
+      <c r="E24" s="2">
+        <v>474</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1719,7 +1719,7 @@
       <c r="D25" s="2">
         <v>1049</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="2">
         <v>1049</v>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       <c r="D26" s="2">
         <v>953</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="2">
         <v>953</v>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       <c r="D27" s="2">
         <v>955</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="2">
         <v>955</v>
       </c>
     </row>
@@ -1768,10 +1768,10 @@
         <v>7</v>
       </c>
       <c r="D28" s="2">
-        <v>351</v>
-      </c>
-      <c r="E28" s="1">
-        <v>351</v>
+        <v>350</v>
+      </c>
+      <c r="E28" s="2">
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1785,10 +1785,10 @@
         <v>7</v>
       </c>
       <c r="D29" s="2">
-        <v>671</v>
-      </c>
-      <c r="E29" s="1">
-        <v>671</v>
+        <v>672</v>
+      </c>
+      <c r="E29" s="2">
+        <v>672</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1804,7 +1804,7 @@
       <c r="D30" s="2">
         <v>398</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="2">
         <v>398</v>
       </c>
     </row>
@@ -1819,10 +1819,10 @@
         <v>7</v>
       </c>
       <c r="D31" s="2">
-        <v>1054</v>
-      </c>
-      <c r="E31" s="1">
-        <v>1054</v>
+        <v>1055</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1055</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1836,10 +1836,10 @@
         <v>7</v>
       </c>
       <c r="D32" s="2">
-        <v>413</v>
-      </c>
-      <c r="E32" s="1">
-        <v>413</v>
+        <v>412</v>
+      </c>
+      <c r="E32" s="2">
+        <v>412</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1853,10 +1853,10 @@
         <v>7</v>
       </c>
       <c r="D33" s="2">
-        <v>987</v>
-      </c>
-      <c r="E33" s="1">
-        <v>987</v>
+        <v>990</v>
+      </c>
+      <c r="E33" s="2">
+        <v>990</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1872,7 +1872,7 @@
       <c r="D34" s="2">
         <v>419</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="2">
         <v>419</v>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       <c r="D35" s="2">
         <v>872</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="2">
         <v>872</v>
       </c>
     </row>
@@ -1904,10 +1904,10 @@
         <v>7</v>
       </c>
       <c r="D36" s="2">
-        <v>2101</v>
-      </c>
-      <c r="E36" s="1">
-        <v>2101</v>
+        <v>2105</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2105</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1921,10 +1921,10 @@
         <v>7</v>
       </c>
       <c r="D37" s="2">
-        <v>407</v>
-      </c>
-      <c r="E37" s="1">
-        <v>407</v>
+        <v>408</v>
+      </c>
+      <c r="E37" s="2">
+        <v>408</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1938,10 +1938,10 @@
         <v>7</v>
       </c>
       <c r="D38" s="2">
-        <v>1170</v>
-      </c>
-      <c r="E38" s="1">
-        <v>1170</v>
+        <v>1171</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1171</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1955,10 +1955,10 @@
         <v>7</v>
       </c>
       <c r="D39" s="2">
-        <v>1539</v>
-      </c>
-      <c r="E39" s="1">
-        <v>1539</v>
+        <v>1461</v>
+      </c>
+      <c r="E39" s="2">
+        <v>1461</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1972,10 +1972,10 @@
         <v>7</v>
       </c>
       <c r="D40" s="2">
-        <v>826</v>
-      </c>
-      <c r="E40" s="1">
-        <v>826</v>
+        <v>952</v>
+      </c>
+      <c r="E40" s="2">
+        <v>952</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1989,10 +1989,10 @@
         <v>7</v>
       </c>
       <c r="D41" s="2">
-        <v>1241</v>
-      </c>
-      <c r="E41" s="1">
-        <v>1241</v>
+        <v>1240</v>
+      </c>
+      <c r="E41" s="2">
+        <v>1240</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2006,10 +2006,10 @@
         <v>7</v>
       </c>
       <c r="D42" s="2">
-        <v>407</v>
-      </c>
-      <c r="E42" s="1">
-        <v>407</v>
+        <v>409</v>
+      </c>
+      <c r="E42" s="2">
+        <v>409</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2023,10 +2023,10 @@
         <v>7</v>
       </c>
       <c r="D43" s="2">
-        <v>334</v>
-      </c>
-      <c r="E43" s="1">
-        <v>334</v>
+        <v>336</v>
+      </c>
+      <c r="E43" s="2">
+        <v>336</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2042,7 +2042,7 @@
       <c r="D44" s="2">
         <v>1212</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="2">
         <v>1212</v>
       </c>
     </row>
@@ -2057,10 +2057,10 @@
         <v>7</v>
       </c>
       <c r="D45" s="2">
-        <v>1424</v>
-      </c>
-      <c r="E45" s="1">
-        <v>1424</v>
+        <v>1425</v>
+      </c>
+      <c r="E45" s="2">
+        <v>1425</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2074,10 +2074,10 @@
         <v>7</v>
       </c>
       <c r="D46" s="2">
-        <v>550</v>
-      </c>
-      <c r="E46" s="1">
-        <v>550</v>
+        <v>549</v>
+      </c>
+      <c r="E46" s="2">
+        <v>549</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2091,10 +2091,10 @@
         <v>7</v>
       </c>
       <c r="D47" s="2">
-        <v>381</v>
-      </c>
-      <c r="E47" s="1">
-        <v>381</v>
+        <v>380</v>
+      </c>
+      <c r="E47" s="2">
+        <v>380</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2108,10 +2108,10 @@
         <v>7</v>
       </c>
       <c r="D48" s="2">
-        <v>1077</v>
-      </c>
-      <c r="E48" s="1">
-        <v>1077</v>
+        <v>1076</v>
+      </c>
+      <c r="E48" s="2">
+        <v>1076</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2127,7 +2127,7 @@
       <c r="D49" s="2">
         <v>351</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="2">
         <v>351</v>
       </c>
     </row>
@@ -2142,10 +2142,10 @@
         <v>7</v>
       </c>
       <c r="D50" s="2">
-        <v>503</v>
-      </c>
-      <c r="E50" s="1">
-        <v>503</v>
+        <v>505</v>
+      </c>
+      <c r="E50" s="2">
+        <v>505</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2159,10 +2159,10 @@
         <v>7</v>
       </c>
       <c r="D51" s="2">
-        <v>603</v>
-      </c>
-      <c r="E51" s="1">
-        <v>603</v>
+        <v>604</v>
+      </c>
+      <c r="E51" s="2">
+        <v>604</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2176,10 +2176,10 @@
         <v>7</v>
       </c>
       <c r="D52" s="2">
-        <v>368</v>
-      </c>
-      <c r="E52" s="1">
-        <v>368</v>
+        <v>369</v>
+      </c>
+      <c r="E52" s="2">
+        <v>369</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2195,7 +2195,7 @@
       <c r="D53" s="2">
         <v>307</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="2">
         <v>307</v>
       </c>
     </row>
@@ -2210,10 +2210,10 @@
         <v>7</v>
       </c>
       <c r="D54" s="2">
-        <v>771</v>
-      </c>
-      <c r="E54" s="1">
-        <v>771</v>
+        <v>769</v>
+      </c>
+      <c r="E54" s="2">
+        <v>769</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2227,10 +2227,10 @@
         <v>7</v>
       </c>
       <c r="D55" s="2">
-        <v>326</v>
-      </c>
-      <c r="E55" s="1">
-        <v>326</v>
+        <v>315</v>
+      </c>
+      <c r="E55" s="2">
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2246,7 +2246,7 @@
       <c r="D56" s="2">
         <v>538</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="2">
         <v>538</v>
       </c>
     </row>
@@ -2261,10 +2261,10 @@
         <v>7</v>
       </c>
       <c r="D57" s="2">
-        <v>221</v>
-      </c>
-      <c r="E57" s="1">
-        <v>221</v>
+        <v>220</v>
+      </c>
+      <c r="E57" s="2">
+        <v>220</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2278,10 +2278,10 @@
         <v>7</v>
       </c>
       <c r="D58" s="2">
-        <v>489</v>
-      </c>
-      <c r="E58" s="1">
-        <v>489</v>
+        <v>491</v>
+      </c>
+      <c r="E58" s="2">
+        <v>491</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2297,7 +2297,7 @@
       <c r="D59" s="2">
         <v>554</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="2">
         <v>554</v>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>7</v>
       </c>
       <c r="D60" s="2">
-        <v>1004</v>
-      </c>
-      <c r="E60" s="1">
-        <v>1004</v>
+        <v>1003</v>
+      </c>
+      <c r="E60" s="2">
+        <v>1003</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2331,7 +2331,7 @@
       <c r="D61" s="2">
         <v>215</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E61" s="2">
         <v>215</v>
       </c>
     </row>
@@ -2346,10 +2346,10 @@
         <v>67</v>
       </c>
       <c r="D62" s="2">
-        <v>617</v>
-      </c>
-      <c r="E62" s="1">
-        <v>617</v>
+        <v>616</v>
+      </c>
+      <c r="E62" s="2">
+        <v>616</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2363,10 +2363,10 @@
         <v>67</v>
       </c>
       <c r="D63" s="2">
-        <v>565</v>
-      </c>
-      <c r="E63" s="1">
-        <v>565</v>
+        <v>564</v>
+      </c>
+      <c r="E63" s="2">
+        <v>564</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2380,10 +2380,10 @@
         <v>67</v>
       </c>
       <c r="D64" s="2">
-        <v>1282</v>
-      </c>
-      <c r="E64" s="1">
-        <v>1282</v>
+        <v>1409</v>
+      </c>
+      <c r="E64" s="2">
+        <v>1409</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2397,10 +2397,10 @@
         <v>67</v>
       </c>
       <c r="D65" s="2">
-        <v>401</v>
-      </c>
-      <c r="E65" s="1">
-        <v>401</v>
+        <v>399</v>
+      </c>
+      <c r="E65" s="2">
+        <v>399</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2416,7 +2416,7 @@
       <c r="D66" s="2">
         <v>307</v>
       </c>
-      <c r="E66" s="1">
+      <c r="E66" s="2">
         <v>307</v>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
       <c r="D67" s="2">
         <v>535</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67" s="2">
         <v>535</v>
       </c>
     </row>
@@ -2448,10 +2448,10 @@
         <v>7</v>
       </c>
       <c r="D68" s="2">
-        <v>288</v>
-      </c>
-      <c r="E68" s="1">
-        <v>288</v>
+        <v>289</v>
+      </c>
+      <c r="E68" s="2">
+        <v>289</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2465,10 +2465,10 @@
         <v>67</v>
       </c>
       <c r="D69" s="2">
-        <v>1729</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1729</v>
+        <v>1089</v>
+      </c>
+      <c r="E69" s="2">
+        <v>1089</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2484,7 +2484,7 @@
       <c r="D70" s="2">
         <v>281</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E70" s="2">
         <v>281</v>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       <c r="D71" s="2">
         <v>296</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E71" s="2">
         <v>296</v>
       </c>
     </row>
@@ -2516,10 +2516,10 @@
         <v>67</v>
       </c>
       <c r="D72" s="2">
-        <v>146</v>
-      </c>
-      <c r="E72" s="1">
-        <v>146</v>
+        <v>145</v>
+      </c>
+      <c r="E72" s="2">
+        <v>145</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2535,7 +2535,7 @@
       <c r="D73" s="2">
         <v>544</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E73" s="2">
         <v>544</v>
       </c>
     </row>
@@ -2550,10 +2550,10 @@
         <v>67</v>
       </c>
       <c r="D74" s="2">
-        <v>333</v>
-      </c>
-      <c r="E74" s="1">
-        <v>333</v>
+        <v>334</v>
+      </c>
+      <c r="E74" s="2">
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2569,7 +2569,7 @@
       <c r="D75" s="2">
         <v>216</v>
       </c>
-      <c r="E75" s="1">
+      <c r="E75" s="2">
         <v>216</v>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       <c r="D76" s="2">
         <v>219</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E76" s="2">
         <v>219</v>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       <c r="D77" s="2">
         <v>282</v>
       </c>
-      <c r="E77" s="1">
+      <c r="E77" s="2">
         <v>282</v>
       </c>
     </row>
